--- a/client_lists/Client List - 04-15-26.xlsx
+++ b/client_lists/Client List - 04-15-26.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24.6640625" customWidth="1" style="4" min="1" max="1"/>
@@ -2446,7 +2446,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Reid, Dom</t>
+          <t>Reid, Dominick</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
